--- a/outputs/monitor_xlsx/20260401.xlsx
+++ b/outputs/monitor_xlsx/20260401.xlsx
@@ -544,10 +544,6 @@
           <t>-2.45%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-3.95%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+4.53%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.21%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+3.54%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.31%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+2.82%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-2.81%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-3.15%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>232.51億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-302.97億</t>
@@ -811,7 +774,6 @@
           <t>101.39億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>24.25億</t>
@@ -822,8 +784,6 @@
           <t>121.24億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>142.46%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.22%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>550.09億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>7308口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8221口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-36.17億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>11.63億</t>
@@ -1020,10 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2035,6 +1978,112 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7290</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E16" t="n">
+        <v>245</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="G16" t="n">
+        <v>147</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-200</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>303</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1470</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-8995</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4429</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="G17" t="n">
+        <v>160</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I17" t="n">
+        <v>322</v>
+      </c>
+      <c r="J17" t="n">
+        <v>155</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2163</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12677</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-106297</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>偏多</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260401.xlsx
+++ b/outputs/monitor_xlsx/20260401.xlsx
@@ -536,14 +536,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31722.99</t>
+          <t>33174.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.45%</t>
-        </is>
-      </c>
+          <t>+4.58%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>307.73</t>
+          <t>321.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3.95%</t>
-        </is>
-      </c>
+          <t>+4.37%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +596,10 @@
           <t>+4.53%</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +622,10 @@
           <t>+0.21%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -624,14 +640,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4812.2$</t>
+          <t>4783.2$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3.54%</t>
-        </is>
-      </c>
+          <t>+2.92%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -654,6 +674,10 @@
           <t>-0.31%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -676,6 +700,10 @@
           <t>+2.82%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +726,10 @@
           <t>-2.81%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -712,14 +744,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>98.19$</t>
+          <t>100.12$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-3.15%</t>
-        </is>
-      </c>
+          <t>-1.24%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -737,24 +773,25 @@
           <t>232.51億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-302.97億</t>
+          <t>-94.97億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1514.83億</t>
+          <t>-474.87億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-417.26億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-8345.16億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -771,19 +808,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>101.39億</t>
-        </is>
-      </c>
+          <t>101.11億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.25億</t>
+          <t>38.12億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>121.24億</t>
-        </is>
-      </c>
+          <t>190.59億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -798,14 +838,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>142.46%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.22%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -820,9 +864,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>550.09億</t>
-        </is>
-      </c>
+          <t>549.82億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,11 +889,15 @@
           <t>7308口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8221口</t>
-        </is>
-      </c>
+          <t>8216口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -862,24 +915,25 @@
           <t>-36.17億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.63億</t>
+          <t>15.86億</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58.14億</t>
+          <t>79.32億</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.12億</t>
+          <t>-9.5億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-82.46億</t>
+          <t>-190.02億</t>
         </is>
       </c>
     </row>
@@ -926,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-302.97億</t>
+          <t>-94.97億</t>
         </is>
       </c>
     </row>
@@ -938,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1514.83億</t>
+          <t>-474.87億</t>
         </is>
       </c>
     </row>
@@ -950,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-417.26億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -962,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-8345.16億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -974,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.25億</t>
+          <t>38.12億</t>
         </is>
       </c>
     </row>
@@ -986,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>121.24億</t>
+          <t>190.59億</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1063,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11.63億</t>
+          <t>15.86億</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1075,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>58.14億</t>
+          <t>79.32億</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.12億</t>
+          <t>-9.5億</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-82.46億</t>
+          <t>-190.02億</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8221口</t>
+          <t>8216口</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1105,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1122,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1201,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1269,10 +1320,10 @@
         <v>5216</v>
       </c>
       <c r="H4" t="n">
-        <v>-268441</v>
+        <v>-205352</v>
       </c>
       <c r="J4" t="n">
-        <v>-1270</v>
+        <v>2400</v>
       </c>
       <c r="K4" t="n">
         <v>14379</v>
@@ -1281,20 +1332,12 @@
         <v>13305</v>
       </c>
       <c r="M4" t="n">
-        <v>68700</v>
+        <v>55813</v>
       </c>
       <c r="N4" t="n">
         <v>-4623758</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1329,13 +1372,13 @@
         <v>1128</v>
       </c>
       <c r="H5" t="n">
-        <v>896</v>
+        <v>859</v>
       </c>
       <c r="I5" t="n">
         <v>-79</v>
       </c>
       <c r="J5" t="n">
-        <v>-1516</v>
+        <v>-1097</v>
       </c>
       <c r="K5" t="n">
         <v>45</v>
@@ -1344,20 +1387,12 @@
         <v>2711</v>
       </c>
       <c r="M5" t="n">
-        <v>13713</v>
+        <v>11062</v>
       </c>
       <c r="N5" t="n">
         <v>-78912</v>
       </c>
-      <c r="O5" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1392,13 +1427,13 @@
         <v>441</v>
       </c>
       <c r="H6" t="n">
-        <v>-3857</v>
+        <v>-8024</v>
       </c>
       <c r="I6" t="n">
         <v>483</v>
       </c>
       <c r="J6" t="n">
-        <v>1215</v>
+        <v>737</v>
       </c>
       <c r="K6" t="n">
         <v>95</v>
@@ -1407,20 +1442,12 @@
         <v>5293</v>
       </c>
       <c r="M6" t="n">
-        <v>28586</v>
+        <v>22468</v>
       </c>
       <c r="N6" t="n">
         <v>-649344</v>
       </c>
-      <c r="O6" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1455,13 +1482,13 @@
         <v>6181</v>
       </c>
       <c r="H7" t="n">
-        <v>-51745</v>
+        <v>-41588</v>
       </c>
       <c r="I7" t="n">
         <v>633</v>
       </c>
       <c r="J7" t="n">
-        <v>3173</v>
+        <v>2526</v>
       </c>
       <c r="K7" t="n">
         <v>408</v>
@@ -1470,20 +1497,12 @@
         <v>26353</v>
       </c>
       <c r="M7" t="n">
-        <v>132664</v>
+        <v>106265</v>
       </c>
       <c r="N7" t="n">
         <v>-6483122</v>
       </c>
-      <c r="O7" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1492,12 +1511,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1506,47 +1525,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2860</v>
+        <v>1660</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="F8" t="n">
-        <v>3039</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>114</v>
+        <v>4304</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-105</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>243</v>
+        <v>385</v>
       </c>
       <c r="J8" t="n">
-        <v>391</v>
+        <v>1274</v>
       </c>
       <c r="K8" t="n">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L8" t="n">
-        <v>1833</v>
+        <v>2113</v>
       </c>
       <c r="M8" t="n">
-        <v>9398</v>
+        <v>8483</v>
       </c>
       <c r="N8" t="n">
-        <v>-89554</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140275</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1555,12 +1566,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1569,47 +1580,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2030</v>
+        <v>1610</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6.84</v>
+        <v>9.9</v>
       </c>
       <c r="F9" t="n">
-        <v>2569</v>
+        <v>4429</v>
       </c>
       <c r="G9" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="H9" t="n">
+        <v>45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-32</v>
+      </c>
+      <c r="J9" t="n">
+        <v>166</v>
+      </c>
+      <c r="K9" t="n">
         <v>155</v>
       </c>
-      <c r="H9" t="n">
-        <v>-996</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>432</v>
-      </c>
-      <c r="K9" t="n">
-        <v>103</v>
-      </c>
       <c r="L9" t="n">
-        <v>3873</v>
+        <v>2163</v>
       </c>
       <c r="M9" t="n">
-        <v>20143</v>
+        <v>10514</v>
       </c>
       <c r="N9" t="n">
-        <v>-19428</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106297</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1618,61 +1621,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1730</v>
+        <v>2860</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>2156</v>
+        <v>3039</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>424</v>
+        <v>114</v>
       </c>
       <c r="H10" t="n">
-        <v>-468</v>
+        <v>-102</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>243</v>
       </c>
       <c r="J10" t="n">
-        <v>872</v>
+        <v>78</v>
       </c>
       <c r="K10" t="n">
-        <v>-2</v>
+        <v>149</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>1833</v>
       </c>
       <c r="M10" t="n">
-        <v>176</v>
+        <v>7432</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89554</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1681,58 +1676,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>375.5</v>
+        <v>2030</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>9.960000000000001</v>
+        <v>6.84</v>
       </c>
       <c r="F11" t="n">
-        <v>1291</v>
+        <v>2569</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="H11" t="n">
-        <v>1763</v>
+        <v>-1067</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1692</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>-1</v>
+        <v>103</v>
       </c>
       <c r="L11" t="n">
-        <v>-124</v>
+        <v>3873</v>
       </c>
       <c r="M11" t="n">
-        <v>-1928</v>
+        <v>15870</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19428</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1741,12 +1731,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1755,47 +1745,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1660</v>
+        <v>7290</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>9.93</v>
+        <v>1.96</v>
       </c>
       <c r="F12" t="n">
-        <v>4304</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>-105</v>
+        <v>245</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>-963</v>
+        <v>89</v>
       </c>
       <c r="I12" t="n">
-        <v>385</v>
+        <v>-53</v>
       </c>
       <c r="J12" t="n">
-        <v>1522</v>
+        <v>-146</v>
       </c>
       <c r="K12" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>2113</v>
+        <v>303</v>
       </c>
       <c r="M12" t="n">
-        <v>11590</v>
+        <v>1167</v>
       </c>
       <c r="N12" t="n">
-        <v>-140275</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8995</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1804,12 +1786,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1818,44 +1800,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>891</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>1035</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="H13" t="n">
-        <v>1105</v>
+        <v>-238</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>2078</v>
+        <v>844</v>
       </c>
       <c r="K13" t="n">
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="L13" t="n">
-        <v>-139</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>-918</v>
+        <v>196</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1864,58 +1841,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-2.59</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>24848</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>231</v>
+        <v>54</v>
       </c>
       <c r="H14" t="n">
-        <v>-7847</v>
+        <v>-1154</v>
       </c>
       <c r="J14" t="n">
+        <v>252</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-124</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-3043</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>42</v>
-      </c>
-      <c r="L14" t="n">
-        <v>8847</v>
-      </c>
-      <c r="M14" t="n">
-        <v>41178</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-145071</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1924,58 +1893,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.6</v>
+        <v>974</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2.39</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>54457</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>-1786</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>401</v>
       </c>
       <c r="H15" t="n">
-        <v>6517</v>
+        <v>321</v>
       </c>
       <c r="J15" t="n">
+        <v>544</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-139</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-916</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>61</v>
-      </c>
-      <c r="L15" t="n">
-        <v>9822</v>
-      </c>
-      <c r="M15" t="n">
-        <v>41899</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-98371</v>
-      </c>
-      <c r="O15" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1984,106 +1945,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>7290</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E16" t="n">
-        <v>245</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="G16" t="n">
-        <v>147</v>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F16" t="n">
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-245</v>
       </c>
       <c r="H16" t="n">
-        <v>-53</v>
+        <v>324</v>
       </c>
       <c r="I16" t="n">
-        <v>-200</v>
+        <v>118</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="K16" t="n">
-        <v>303</v>
+        <v>-23</v>
       </c>
       <c r="L16" t="n">
-        <v>1470</v>
+        <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>-8995</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1610</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4429</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>525</v>
-      </c>
-      <c r="G17" t="n">
-        <v>160</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-32</v>
-      </c>
-      <c r="I17" t="n">
-        <v>322</v>
-      </c>
-      <c r="J17" t="n">
-        <v>155</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2163</v>
-      </c>
-      <c r="L17" t="n">
-        <v>12677</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-106297</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>偏多</t>
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260401.xlsx
+++ b/outputs/monitor_xlsx/20260401.xlsx
@@ -544,10 +544,6 @@
           <t>+4.58%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+4.37%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+4.53%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.21%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+2.92%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.31%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+2.82%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-2.81%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-1.24%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>232.51億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-94.97億</t>
@@ -811,7 +774,6 @@
           <t>101.11億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>38.12億</t>
@@ -822,8 +784,6 @@
           <t>190.59億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.22%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>549.82億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>7308口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8216口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-36.17億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>15.86億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1995,6 +1939,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>405</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8949</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G17" t="n">
+        <v>53</v>
+      </c>
+      <c r="H17" t="n">
+        <v>788</v>
+      </c>
+      <c r="I17" t="n">
+        <v>787</v>
+      </c>
+      <c r="J17" t="n">
+        <v>96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8262</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31508</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22035</v>
+      </c>
+      <c r="N17" t="n">
+        <v>19.94</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260401.xlsx
+++ b/outputs/monitor_xlsx/20260401.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,20 +1250,23 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.45</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>4.28</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>130698</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>5216</v>
       </c>
       <c r="H4" t="n">
-        <v>-205352</v>
+        <v>-260250</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>2400</v>
@@ -1276,11 +1278,14 @@
         <v>13305</v>
       </c>
       <c r="M4" t="n">
-        <v>55813</v>
+        <v>69118</v>
       </c>
       <c r="N4" t="n">
         <v>-4623758</v>
       </c>
+      <c r="O4" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1303,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>812</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>3.18</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>3433</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1128</v>
       </c>
       <c r="H5" t="n">
-        <v>859</v>
+        <v>1194</v>
       </c>
       <c r="I5" t="n">
         <v>-79</v>
       </c>
       <c r="J5" t="n">
-        <v>-1097</v>
+        <v>-1599</v>
       </c>
       <c r="K5" t="n">
         <v>45</v>
@@ -1331,11 +1336,14 @@
         <v>2711</v>
       </c>
       <c r="M5" t="n">
-        <v>11062</v>
+        <v>13773</v>
       </c>
       <c r="N5" t="n">
         <v>-78912</v>
       </c>
+      <c r="O5" t="n">
+        <v>-9.380000000000001</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1475</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>6.88</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>12559</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>441</v>
       </c>
       <c r="H6" t="n">
-        <v>-8024</v>
+        <v>-9856</v>
       </c>
       <c r="I6" t="n">
         <v>483</v>
       </c>
       <c r="J6" t="n">
-        <v>737</v>
+        <v>1502</v>
       </c>
       <c r="K6" t="n">
         <v>95</v>
@@ -1386,11 +1394,14 @@
         <v>5293</v>
       </c>
       <c r="M6" t="n">
-        <v>22468</v>
+        <v>27761</v>
       </c>
       <c r="N6" t="n">
         <v>-649344</v>
       </c>
+      <c r="O6" t="n">
+        <v>4.41</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1413,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1855</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>5.4</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>46457</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>6181</v>
       </c>
       <c r="H7" t="n">
-        <v>-41588</v>
+        <v>-46543</v>
       </c>
       <c r="I7" t="n">
         <v>633</v>
       </c>
       <c r="J7" t="n">
-        <v>2526</v>
+        <v>3541</v>
       </c>
       <c r="K7" t="n">
         <v>408</v>
@@ -1441,11 +1452,14 @@
         <v>26353</v>
       </c>
       <c r="M7" t="n">
-        <v>106265</v>
+        <v>132618</v>
       </c>
       <c r="N7" t="n">
         <v>-6483122</v>
       </c>
+      <c r="O7" t="n">
+        <v>0.35</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1660</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>9.93</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>4304</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-105</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>-676</v>
       </c>
       <c r="I8" t="n">
         <v>385</v>
       </c>
       <c r="J8" t="n">
-        <v>1274</v>
+        <v>1713</v>
       </c>
       <c r="K8" t="n">
         <v>68</v>
@@ -1496,11 +1510,14 @@
         <v>2113</v>
       </c>
       <c r="M8" t="n">
-        <v>8483</v>
+        <v>10596</v>
       </c>
       <c r="N8" t="n">
         <v>-140275</v>
       </c>
+      <c r="O8" t="n">
+        <v>8.23</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1610</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.9</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>4429</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>525</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="I9" t="n">
         <v>-32</v>
       </c>
       <c r="J9" t="n">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="K9" t="n">
         <v>155</v>
@@ -1551,11 +1568,14 @@
         <v>2163</v>
       </c>
       <c r="M9" t="n">
-        <v>10514</v>
+        <v>12677</v>
       </c>
       <c r="N9" t="n">
         <v>-106297</v>
       </c>
+      <c r="O9" t="n">
+        <v>6.82</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2860</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3039</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>114</v>
       </c>
       <c r="H10" t="n">
-        <v>-102</v>
+        <v>-472</v>
       </c>
       <c r="I10" t="n">
         <v>243</v>
       </c>
       <c r="J10" t="n">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="K10" t="n">
         <v>149</v>
@@ -1606,11 +1626,14 @@
         <v>1833</v>
       </c>
       <c r="M10" t="n">
-        <v>7432</v>
+        <v>9265</v>
       </c>
       <c r="N10" t="n">
         <v>-89554</v>
       </c>
+      <c r="O10" t="n">
+        <v>7.64</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2030</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>6.84</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>2569</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>155</v>
       </c>
       <c r="H11" t="n">
-        <v>-1067</v>
+        <v>-1064</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="K11" t="n">
         <v>103</v>
@@ -1661,11 +1684,14 @@
         <v>3873</v>
       </c>
       <c r="M11" t="n">
-        <v>15870</v>
+        <v>19743</v>
       </c>
       <c r="N11" t="n">
         <v>-19428</v>
       </c>
+      <c r="O11" t="n">
+        <v>7.19</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1688,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7290</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1.96</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>245</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="I12" t="n">
         <v>-53</v>
       </c>
       <c r="J12" t="n">
-        <v>-146</v>
+        <v>-200</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
@@ -1716,11 +1742,14 @@
         <v>303</v>
       </c>
       <c r="M12" t="n">
-        <v>1167</v>
+        <v>1470</v>
       </c>
       <c r="N12" t="n">
         <v>-8995</v>
       </c>
+      <c r="O12" t="n">
+        <v>6.55</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>424</v>
       </c>
       <c r="H13" t="n">
-        <v>-238</v>
+        <v>-26</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>844</v>
+        <v>875</v>
       </c>
       <c r="K13" t="n">
         <v>-2</v>
@@ -1771,11 +1800,14 @@
         <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,20 +1830,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>54</v>
       </c>
       <c r="H14" t="n">
-        <v>-1154</v>
+        <v>-1315</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>252</v>
@@ -1823,11 +1858,14 @@
         <v>-124</v>
       </c>
       <c r="M14" t="n">
-        <v>-3043</v>
+        <v>-3167</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1850,23 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>401</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>1646</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>544</v>
+        <v>890</v>
       </c>
       <c r="K15" t="n">
         <v>-19</v>
@@ -1875,11 +1916,14 @@
         <v>-139</v>
       </c>
       <c r="M15" t="n">
-        <v>-916</v>
+        <v>-1055</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1902,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-245</v>
       </c>
       <c r="H16" t="n">
-        <v>324</v>
+        <v>-37</v>
       </c>
       <c r="I16" t="n">
         <v>118</v>
       </c>
       <c r="J16" t="n">
-        <v>-10</v>
+        <v>108</v>
       </c>
       <c r="K16" t="n">
         <v>-23</v>
@@ -1930,11 +1974,14 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1952,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>405</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>9.91</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>8949</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-113</v>
       </c>
-      <c r="G17" t="n">
-        <v>53</v>
-      </c>
       <c r="H17" t="n">
+        <v>-509</v>
+      </c>
+      <c r="I17" t="n">
         <v>788</v>
       </c>
-      <c r="I17" t="n">
-        <v>787</v>
-      </c>
       <c r="J17" t="n">
+        <v>1119</v>
+      </c>
+      <c r="K17" t="n">
         <v>96</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8262</v>
       </c>
-      <c r="L17" t="n">
-        <v>31508</v>
-      </c>
       <c r="M17" t="n">
+        <v>39277</v>
+      </c>
+      <c r="N17" t="n">
         <v>-22035</v>
       </c>
-      <c r="N17" t="n">
-        <v>19.94</v>
+      <c r="O17" t="n">
+        <v>18.23</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260401.xlsx
+++ b/outputs/monitor_xlsx/20260401.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>18.23</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11745</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-3537</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-6104</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1946</v>
+      </c>
+      <c r="K18" t="n">
+        <v>461</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6375</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31144</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400971</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-11.84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8025</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-240</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-2258</v>
+      </c>
+      <c r="I19" t="n">
+        <v>79</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1018</v>
+      </c>
+      <c r="K19" t="n">
+        <v>235</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30667</v>
+      </c>
+      <c r="M19" t="n">
+        <v>154303</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393870</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>574</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17700</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>1743</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3744</v>
+      </c>
+      <c r="I20" t="n">
+        <v>425</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5129</v>
+      </c>
+      <c r="K20" t="n">
+        <v>304</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8298</v>
+      </c>
+      <c r="M20" t="n">
+        <v>43139</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160917</v>
+      </c>
+      <c r="O20" t="n">
+        <v>10.54</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
